--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:03:37+00:00</t>
+    <t>2025-02-11T12:08:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -676,7 +676,9 @@
     <t>Reliabilility of the identity | Fiabilité de l'identité</t>
   </si>
   <si>
-    <t>Reliabilility of the patient's identity | Précision sur le degré de fiabilité de l'identité du patient (si provisoire, validé... avec la justification : quelle type de pièce d'identité ?) avec la méthode de collection</t>
+    <t>Précision sur le degré de fiabilité de l'identité du patient (si provisoire, validé... avec la justification : quelle type de pièce d'identité ?) accompagné de la méthode de collection.
++Reliabilility of the patient's identity</t>
   </si>
   <si>
     <t>Patient.extension:deathPlace</t>
@@ -692,7 +694,9 @@
     <t>FR Core Patient Death Place Extension</t>
   </si>
   <si>
-    <t>Carries the death place of the patient |Précise le lieu de décès du patient (hôpital, sur la voie publique, au domicile, etc.).</t>
+    <t>Précise le lieu de décès du patient (hôpital, sur la voie publique, au domicile, etc.).
++Carries the death place of the patient</t>
   </si>
   <si>
     <t>Patient.extension:birthdateUpdateIndicator</t>
@@ -805,7 +809,8 @@
     <t>FR Core Address Insee Code Extension</t>
   </si>
   <si>
-    <t>This extension adds the insee code (5 digits) to the address | Ajout du code insee (5 chiffres) à l'adresse postale</t>
+    <t>Extension d'ajout du code insee (5 chiffres) à l'adresse postale.
+This extension adds the insee code (5 digits) to the address</t>
   </si>
   <si>
     <t>Patient.extension:birthPlace.value[x].use</t>
@@ -2298,10 +2303,12 @@
 </t>
   </si>
   <si>
-    <t>Contact identifier in the patient resource | Identifiant de contact dans la ressource Patient</t>
-  </si>
-  <si>
-    <t>This extension carries the contact identifier in the patient resource | Ajout d'un identifiant de contact dans la ressource Patient</t>
+    <t>FR Core Patient Contact Identifier Extension</t>
+  </si>
+  <si>
+    <t>Identifiant de contact dans la ressource Patient
++This extension carries the contact identifier in the patient resource</t>
   </si>
   <si>
     <t>Patient.contact.extension:comment</t>
@@ -2317,7 +2324,8 @@
     <t>Comment on a dataElement | Commentaire sur un dataElement</t>
   </si>
   <si>
-    <t>add a comment on a dataElement  of a resource | Ajout d'un commentaire sur un dataElement d'une ressource</t>
+    <t>Ajout d'un commentaire sur un dataElement d'une ressource.
+Add a comment on a dataElement  of a resource</t>
   </si>
   <si>
     <t>Patient.contact.modifierExtension</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:08:53+00:00</t>
+    <t>2025-02-11T15:31:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:31:42+00:00</t>
+    <t>2025-02-11T17:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T17:07:06+00:00</t>
+    <t>2025-02-11T17:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T17:08:15+00:00</t>
+    <t>2025-02-11T17:29:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
